--- a/public/sap-reporting/expansion-150-downloads/EXT-FI19-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI19-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R7fbf803a1f8240af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Re748c0ab91dc4b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R288aa33d389c4575"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Ra9017adb360a4d2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R20e12ddbee32416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rb7d1a968911848cb"/>
   </x:sheets>
 </x:workbook>
 </file>
